--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260825.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260825.xlsx
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>275,095,168</t>
+          <t>71,932,792</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>71,932,792</t>
+          <t>275,095,168</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>260,843,906</t>
+          <t>115,129,818</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>115,129,818</t>
+          <t>260,843,906</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>216,247,976</t>
+          <t>4,159,168</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>4,159,168</t>
+          <t>216,247,976</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
